--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,171 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep01/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-31 18:10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/052236a5567bc5ca3adce4d358aa1b6d_1785521290.mp4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-31 18:14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ca8653f75c031e9090448ef4da73989c_1785521511.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-31 18:16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aa3c7769a6f0123a84132ae37a1a121b_1785521769.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep02/shots/shot_03.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,171 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-01 17:35</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4937984e2e021e9bffa804727f017d86_1785605723.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-01 17:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5a255b78b25ae2e1749dcae48d3fcc83_1785605842.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-01 17:41</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/904825abb276632f29af346cb1f0f865_1785606062.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep03/shots/shot_03.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +982,171 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-02 17:36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5618e9f37f5d46f65500b023429c10b3_1785692159.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-02 17:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b447afac5d52397da2bf027871c030f8_1785692287.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 17:40</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fc9c6bd2e230b8191b64cf0c3699252d_1785692401.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,171 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 18:21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/73b1df77fcb1f2203dee715916110fb6_1785781243.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-03 18:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0245d569958db9ddf4917c2a2f516f2e_1785781380.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-03 18:25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a8933b817a8f7dfe1f4a120aebbca853_1785781491.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,171 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-07 17:28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a73b77807d37dde4c3d6c9f9ce62e8b4_1786123690.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-07 17:34</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/47dceea15c2e9cf89ccde450a1411ee7_1786123828.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-07 17:36</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e2dc4e27d5e293c5c1ef47ae1654856d_1786124184.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,171 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-08 17:06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dac3180ed933bb5b238bca52adf942fb_1786208744.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-08 17:08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/520bb12f0150602a732c009b54b42ca5_1786208865.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-08 17:10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/42daad993c776c1e2dfe1941fc46e9cf_1786208988.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,6 +1642,171 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-09 17:08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/56c01fd266a2e0e4bf7d90e69b10e6e2_1786295255.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-09 17:10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e14fab3929cbc1d0b23a84563857b845_1786295388.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-09 17:12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3d579ddb8f6196664d8fe1c221721c7c_1786295524.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,6 +1807,171 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-13 17:33</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/503b65874553f157fafa73f3daff2c79_1786642367.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-13 17:35</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9d9032947b53f72d1eef5953049dc3b0_1786642501.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-13 17:40</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d2940d7e97298db38c1c5c51a24e736e_1786642641.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,6 +1972,171 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:36</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/21dfad010c1fe1cab125e0f0728f5358_1786728953.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:39</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3400b54287d497fd465182d20878aab6_1786729107.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:43</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/268cf10e4f1595671559fa68366f6942_1786729219.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,6 +2137,171 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:54</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/db25728ccb19bbc91ea432438e6fcf3c_1786812862.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:58</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e874c744b405262ecef26203f2a2decd_1786812974.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep11/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/00b5b672fe3e0d0bcf2c2388baf336b1_1786813217.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep11/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2302,6 +2302,171 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-16 16:55</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a220888033c7488a6129b86a09302e5c_1786899295.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-16 16:57</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ac59738743946fac8eb11e6acfcd5a39_1786899407.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep12/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-16 17:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/69a8a27578b78567d6cb88fff5bf9f54_1786899529.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep12/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2467,6 +2467,171 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-17 17:02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2dad25f75c2d9a422888ee24b7350f75_1786985977.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-17 17:04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b875f660b5aecf6660125f78b895f4fb_1786986253.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep13/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-17 17:07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3068485f997e3155d65130d8d0931439_1786986396.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep13/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,171 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-18 17:33</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e071524e5c0b09d54945950d7a06f4b0_1787074364.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep14/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-18 17:39</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/49d5026e3a5df26c0483d4e5f712f6e4_1787074491.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep14/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-18 17:46</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1cd04e4d0ab90731b99014392bd36c6c_1787074869.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep14/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2797,6 +2797,171 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c4e14f8815047e8a4513541437e1d75e_1787245497.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep15/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4765c48e30e9077de95bd67a56bc2c5c_1787245654.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep15/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7b51fae3f2f18eb7896cc6c2a5293c81_1787245764.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep15/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,6 +2962,171 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:05</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ce292c51bab04c6aebfc3a4273bba52d_1787331869.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep16/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cb30bb1b18798f7d4e1cc67121ef1f5c_1787331996.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep16/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/31d4912b161a831b21537826316f7386_1787332217.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep16/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3127,6 +3127,171 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-22 16:57</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b4a90f3aa5443d5f42f82906dd3b827a_1787417671.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep17/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-22 17:01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/17a42da9bb32584c8de4db05f70b8663_1787417967.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep17/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-22 17:06</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/900694bedbd533c9fb75fde1b94a532f_1787418184.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep17/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3292,6 +3292,171 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:55</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9e1e90aa3df9b0de96a4a2221a331236_1787504118.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep18/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:57</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b6601462f3c63d965ca302ea16823138_1787504238.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep18/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:59</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4d49364ef58c63a8f17fce45bd00251a_1787504360.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep18/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,171 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:08</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cb99ae8527d643f539831344b0429dc8_1787591292.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep19/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5d570dd2a8787467488468599a33531d_1787591417.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep19/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-24 17:12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6b70829985dd16c6e2c6b01cfa6a4dff_1787591544.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep19/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3622,6 +3622,171 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-25 17:10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7d0efeb4cc8c966d1083cd7bb30ebf41_1787677807.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep20/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-25 17:12</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/df67725a7da5574758db11b072a9a3d1_1787677941.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep20/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-25 17:15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aa42e6afc993e07471152c6750547fa5_1787678076.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep20/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3787,6 +3787,171 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-26 18:24</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2d35da19c34db8b0d243abe28da90770_1787768486.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep21/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-26 18:26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2795edb7a36cb4fbe90444d1845c2827_1787768782.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep21/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-26 18:33</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ac37c851ce5f2625c8d1900a269cf683_1787768899.mp4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep21/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3952,6 +3952,171 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-28 01:06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d7ec91d8591a18adf7efabab235ad254_1787879184.mp4</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep22/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-28 01:08</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/082c5e7afc0bd54ddc67f28994bd5eb3_1787879290.mp4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep22/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-28 01:10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dd56860894b9fb2dc5cc589d7e8ca60d_1787879429.mp4</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep22/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4117,6 +4117,171 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:42</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/62969eb04ba00409beda5399b71dec7c_1787964001.mp4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep23/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:47</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6a18f790e9d1e788c1f0009d47d61838_1787964265.mp4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep23/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:58</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c6d830260ef51dbed721dcffafb484cd_1787964544.mp4</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep23/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4282,6 +4282,171 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-30 19:29</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/376a705ac3e87d10e77c5e0cc731907c_1788117948.mp4</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep24/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-30 19:32</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8aa8f1e9bb6812e7750415266f64b704_1788118300.mp4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep24/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-30 19:37</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ae021e6bf409a653f14200ea2514f217_1788118425.mp4</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep24/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4447,6 +4447,171 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:45</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ee678622c955c4f6ac174f3c4720e566_1788212726.mp4</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep25/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:47</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/460bcc98a0a8f3490843dbd0eaf9a03a_1788212826.mp4</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep25/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:49</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/eeca026698130ce07e3d664ff7cc42e6_1788212921.mp4</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep25/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4612,6 +4612,171 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:35</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/905bbf7166ddc90c00a4475e27c84896_1788554073.mp4</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep26/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:38</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/af525e3da33c01124b71c323fae5a550_1788554180.mp4</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep26/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:40</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6d9c9ac595ead5bff6502b51c524e3c2_1788554393.mp4</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep26/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4777,6 +4777,171 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-05 18:33</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ef2cbc0d44953d503f21312b07b6aeb3_1788633161.mp4</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep27/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-05 18:35</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b46f7dabaca8b6ee010240b7cfba270b_1788633271.mp4</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep27/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-05 18:38</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a68c700d4202fd06dd34d1eb64fc021e_1788633391.mp4</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep27/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4942,6 +4942,171 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-06 18:39</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fc083780e1914d8d6735fd4945a0813a_1788719785.mp4</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep28/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-06 18:41</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0274bf625d9ca1182706550c2c8e71a3_1788720062.mp4</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep28/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-06 18:43</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4bcb021043211331c5b141a09355de6c_1788720188.mp4</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep28/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5107,6 +5107,171 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:08</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6fa04c990b935a99852f9c820befc68e_1788811686.mp4</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep29/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/48944e6750f3096c16985243ed411e5a_1788811834.mp4</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep29/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:14</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dd0525f03d9eec4c4d49cce65b82cdf1_1788811954.mp4</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep29/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5272,6 +5272,171 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-08 19:34</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/73572f3d4238065f9d6c67d645c22783_1788896047.mp4</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep30/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-08 19:36</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/35c369c43bba00d0378b5518ac4336d1_1788896141.mp4</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep30/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-08 19:37</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/059780b1ace358f5d35dfeb181ade569_1788896244.mp4</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep30/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5437,6 +5437,171 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/60e51e3e72570235787f0398ebf835be_1788981928.mp4</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep31/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:28</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fdca5f53ffe8ec4044540d2c4a0f843a_1788982058.mp4</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep31/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5cca923cd0bc9ab766e69b1eb7d09bc5_1788982179.mp4</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep31/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5602,6 +5602,171 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:15</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b29db83dd9356be750cc0b19f94b10f0_1789067673.mp4</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep32/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:17</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dacbef6d7a691c0590f87c2a681fcaff_1789067794.mp4</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep32/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:19</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e9f8ec4ec3ef8b846fa789f6806e4d70_1789067928.mp4</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep32/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/event-horizon/series_log.xlsx
+++ b/galactic_experience/event-horizon/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5767,6 +5767,336 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/701fc03b6ba76b8476546504dc820fd8_1789092688.mp4</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projeler\Youtube\output\series\event-horizon\episodes\ep33\shots\shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:13</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f148a5e5e6570ea159383ae44d1afe53_1789092802.mp4</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projeler\Youtube\output\series\event-horizon\episodes\ep33\shots\shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:15</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a08b2c7fbfe400caece85fd4658996b8_1789092900.mp4</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projeler\Youtube\output\series\event-horizon\episodes\ep33\shots\shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:40</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/11f91afd8e403a03698046b1bdae5ba8_1789238390.mp4</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep34/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:42</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a129361731fe7ebc0d16123ff8865ed0_1789238503.mp4</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep34/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:44</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0e8aa31dd88d204364d07b792e15417c_1789238618.mp4</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/event-horizon/episodes/ep34/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
